--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,4927 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>18.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14 811</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>18.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>15 706</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25 491</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lissorgue R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16 354</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Turpin C.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14 250</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>14 755</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14 962</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="BG9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23 167</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="BG10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>551</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dvUee9dD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17.08.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="BG11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EeC5phre</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="BG12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4 918</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="BG13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Gabriel Montpied
+ (Clermont-Ferrand)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10 800</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5 582</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="BG14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="BG15" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="BG16" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="BG17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>555</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,827 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OA5YizjL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>19.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>lEQmcVR0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Petit A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Saint-Symphorien
+ (Metz)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28 786</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,501 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,861 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>63 841</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0pvInj5s</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Bauer
+ (Paris - Saint-Ouen)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4 560</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ3"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,60 +676,70 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
           <t>total_passes_home</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>total_passes_away</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_home</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_away</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>tackles_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>tackles_away</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_home</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_away</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_home</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_away</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>interceptions_home</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>interceptions_away</t>
         </is>
@@ -738,234 +748,230 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2024 15:45</t>
+          <t>30.08.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ben El Hadj Salem H.
+          <t>Leonard T.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>67 394</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>63 841</t>
-        </is>
-      </c>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>de zerbi roberto</t>
+          <t>sage pierre</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>elsner luka</t>
+          <t>rosenior liam</t>
         </is>
       </c>
       <c r="AU2" t="n">
@@ -994,214 +1000,212 @@
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0pvInj5s</t>
+          <t>WlzDg17E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.08.2024 15:45</t>
+          <t>30.08.2024 15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bouille T.
+          <t>Petit A.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Bauer
- (Paris - Saint-Ouen)</t>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>4 560</t>
-        </is>
-      </c>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
+          <t>2aeoANM8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>AC Ajaccio</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>fsfAHubD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AC Ajaccio</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>8tmnzqxe</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>poirier gregory</t>
+          <t>chabert mathieu</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>chabert mathieu</t>
+          <t>dumont stephane</t>
         </is>
       </c>
       <c r="AU3" t="n">
@@ -1220,62 +1224,1764 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Gabriel Montpied
+ (Clermont-Ferrand)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10 800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,94 +676,48 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>total_passes_home</t>
+          <t>red_cards_home</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>tackles_home</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>tackles_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>clearances_completed_home</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>clearances_completed_away</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_home</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_away</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_home</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_away</t>
+          <t>red_cards_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2024 14:00</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Millot B.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20 484</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45 434</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
@@ -776,192 +730,192 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>der zakarian michel</t>
+          <t>genesio bruno</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>kombouare antoine</t>
+          <t>luis enrique</t>
         </is>
       </c>
       <c r="AU2" t="n">
@@ -980,244 +934,238 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.08.2024 12:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Stinat J.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15 220</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9 168</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>roy eric</t>
+          <t>dujeux alexandre</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>dall oglio olivier</t>
+          <t>haise franck</t>
         </is>
       </c>
       <c r="AU3" t="n">
@@ -1234,225 +1182,255 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zoZtwwYp</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 09:30</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gaillouste P.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade de la Licorne
- (Amiens)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12 097</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5 460</t>
+          <t>19 715</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>lKkBAsxF</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>jgNAYRGi</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>daf omar</t>
+          <t>digard didier</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>pantaloni olivier</t>
+          <t>pelissier christophe</t>
         </is>
       </c>
       <c r="AU4" t="n">
         <v>55</v>
       </c>
       <c r="AV4" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1464,279 +1442,249 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8lUzaKf4</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.08.2024 09:30</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Batta F.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Saint-Symphorien
- (Metz)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28 786</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>18 369</t>
-        </is>
-      </c>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>E1wDrLsJ</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Laval</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>le mignan stephane</t>
+          <t>elsner luka</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>frapolli olivier</t>
+          <t>stephan julien</t>
         </is>
       </c>
       <c r="AU5" t="n">
         <v>55</v>
       </c>
       <c r="AV5" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1746,64 +1694,514 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9 030</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19 178</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2905 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>19.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lissorgue R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>551</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>551</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7 246</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>551</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xlCidXdD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Taleb A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5 956</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>lbfDWDYP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Armand Cesari
+ (Bastia)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16 048</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9 967</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d47R8AtJ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Benchabane F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5 916</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4zEqbgS0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8 112</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8UeBChsf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade Francis Le Basser
+ (Laval)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11 017</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5 948</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>88Kz0Fcl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade Francis Turcan
+ (Martigues)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11 500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>nF72EECs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Bauer
+ (Paris - Saint-Ouen)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4 643</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>555</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -678,230 +678,234 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2g2J0IEs</t>
+          <t>f5f1oGre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.10.2024 15:45</t>
+          <t>22.10.2024 14:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kubler G.
+          <t>Gaillouste P.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade de l'Aube
- (Troyes)</t>
+          <t>Nouste Camp
+ (Pau)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20 420</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>4 031</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3 431</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>fsfAHubD</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Troyes</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0OEHEprs</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Paris FC</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>dumont stephane</t>
+          <t>usai nicolas</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>gilli stephane</t>
+          <t>tavenot benoit</t>
         </is>
       </c>
       <c r="AU2" t="n">

--- a/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,505 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>4WNXteh2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>04.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Buquet R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2 757</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>